--- a/naver-place-crawler/results_health/화성_PT.xlsx
+++ b/naver-place-crawler/results_health/화성_PT.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="37" customWidth="1" min="8" max="8"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="Q2" t="n">
-        <v>6096</v>
+        <v>6246</v>
       </c>
       <c r="R2" t="n">
-        <v>7137</v>
+        <v>7290</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -718,10 +718,10 @@
         <v>223</v>
       </c>
       <c r="Q3" t="n">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="R3" t="n">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="Q4" t="n">
-        <v>2486</v>
+        <v>2024</v>
       </c>
       <c r="R4" t="n">
-        <v>3190</v>
+        <v>2731</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -846,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>여성전용 올더핏 PT&amp;필라테스 병점동탄점</t>
+          <t>밸런스핏 PT&amp;헬스 동탄병점역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>allthefit_bj@naver.com</t>
+          <t>balancelab_pt@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1354-1478</t>
+          <t>0507-1368-9549</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 화성시 병점구 병점노을4로 5 10층</t>
+          <t>경기도 화성시 병점구 병점노을4로 19 골든스퀘어원 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_giRiG</t>
+          <t>https://www.instagram.com/balancefit_pt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -894,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>132</v>
+        <v>27</v>
       </c>
       <c r="Q5" t="n">
-        <v>541</v>
+        <v>190</v>
       </c>
       <c r="R5" t="n">
-        <v>673</v>
+        <v>217</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1442656447</t>
+          <t>2050262388</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1442656447</t>
+          <t>https://m.place.naver.com/place/2050262388</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -940,25 +940,33 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>프로핏97 PT 동탄1호점</t>
+          <t>피지오스튜디오 필라테스 &amp; PT 동탄호수공원점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ryn8118@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>physiostudio2021@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>contact@physiostudio.co.kr</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1350-7099</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄기흥로520번나길 18 101호</t>
+          <t>경기도 화성시 동탄구 동탄대로5길 21 2층 E203, E204호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_WaFeK</t>
+          <t>https://www.physiostudio.co.kr/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -973,7 +981,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -984,7 +992,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -993,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>642</v>
+        <v>74</v>
       </c>
       <c r="Q6" t="n">
-        <v>1904</v>
+        <v>206</v>
       </c>
       <c r="R6" t="n">
-        <v>2546</v>
+        <v>280</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1299138186</t>
+          <t>2075538417</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1299138186</t>
+          <t>https://m.place.naver.com/place/2075538417</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1030,34 +1038,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>더제이피트니스앤필라테스 향남2지구점</t>
+          <t>비전휘트니스 동탄점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jsixgym2@naver.com</t>
+          <t>visionfitness4@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1394-8826</t>
+          <t>0507-1352-4687</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 화성시 만세구 향남읍 상신하길로298번길 7-23 케이티시네마2동 8층</t>
+          <t>경기도 화성시 동탄구 동탄중심상가2길 26-31 가희프라자 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jsixgym2</t>
+          <t>https://litt.ly/visionfitness4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1067,7 +1075,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1087,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1204</v>
+        <v>2191</v>
       </c>
       <c r="Q7" t="n">
-        <v>1453</v>
+        <v>5108</v>
       </c>
       <c r="R7" t="n">
-        <v>2657</v>
+        <v>7299</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1286475967</t>
+          <t>1525661824</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1286475967</t>
+          <t>https://m.place.naver.com/place/1525661824</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1181,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1619</v>
+        <v>1660</v>
       </c>
       <c r="Q8" t="n">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="R8" t="n">
-        <v>2260</v>
+        <v>2307</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1206,7 +1214,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1275,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1562</v>
+        <v>1590</v>
       </c>
       <c r="Q9" t="n">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="R9" t="n">
-        <v>2552</v>
+        <v>2587</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1300,46 +1308,46 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>봉담헬스PT피트니스M</t>
+          <t>어테인 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fitness0221@naver.com</t>
+          <t>chlwlgns6849@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1355-4598</t>
+          <t>0507-1413-5543</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 화성시 효행구 봉담읍 상봉길 31 3층 304호, 305호, 306호</t>
+          <t>경기도 화성시 효행구 봉담읍 상리3길 43-18 지음프라자2, 501호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_ximHWn</t>
+          <t>https://blog.naver.com/chlwlgns6849</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1349,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1360,7 +1368,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1369,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>439</v>
+        <v>126</v>
       </c>
       <c r="Q10" t="n">
-        <v>680</v>
+        <v>213</v>
       </c>
       <c r="R10" t="n">
-        <v>1119</v>
+        <v>339</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,51 +1392,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1836647807</t>
+          <t>1207439300</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1836647807</t>
+          <t>https://m.place.naver.com/place/1207439300</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>어테인 PT</t>
+          <t>파워맥스짐 헬스&amp;PT 병점본점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>chlwlgns6849@naver.com</t>
+          <t>powermaxgym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1413-5543</t>
+          <t>0507-1394-6202</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 화성시 효행구 봉담읍 상리3길 43-18 지음프라자2, 501호</t>
+          <t>경기도 화성시 병점구 병점노을7로 5 603호~609호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chlwlgns6849</t>
+          <t>https://www.instagram.com/power_max_gym?igshid=OGQ5ZDc2ODk2ZA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1443,7 +1451,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1463,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>125</v>
+        <v>2687</v>
       </c>
       <c r="Q11" t="n">
-        <v>208</v>
+        <v>1023</v>
       </c>
       <c r="R11" t="n">
-        <v>333</v>
+        <v>3710</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,17 +1486,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1207439300</t>
+          <t>1941293926</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1207439300</t>
+          <t>https://m.place.naver.com/place/1941293926</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/화성_PT.xlsx
+++ b/naver-place-crawler/results_health/화성_PT.xlsx
@@ -426,7 +426,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="Q2" t="n">
-        <v>6246</v>
+        <v>6248</v>
       </c>
       <c r="R2" t="n">
-        <v>7290</v>
+        <v>7293</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q3" t="n">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="R3" t="n">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -812,10 +812,10 @@
         <v>707</v>
       </c>
       <c r="Q4" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="R4" t="n">
-        <v>2731</v>
+        <v>2732</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -846,34 +846,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>밸런스핏 PT&amp;헬스 동탄병점역점</t>
+          <t>피지오스튜디오 필라테스 &amp; PT 동탄호수공원점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>balancelab_pt@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>physiostudio2021@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>contact@physiostudio.co.kr</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1368-9549</t>
+          <t>0507-1350-7099</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 화성시 병점구 병점노을4로 19 골든스퀘어원 3층</t>
+          <t>경기도 화성시 동탄구 동탄대로5길 21 2층 E203, E204호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/balancefit_pt</t>
+          <t>https://www.physiostudio.co.kr/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +887,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="Q5" t="n">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="R5" t="n">
-        <v>217</v>
+        <v>283</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2050262388</t>
+          <t>2075538417</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2050262388</t>
+          <t>https://m.place.naver.com/place/2075538417</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -940,38 +944,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피지오스튜디오 필라테스 &amp; PT 동탄호수공원점</t>
+          <t>밸런스핏 PT&amp;헬스 동탄병점역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>physiostudio2021@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>contact@physiostudio.co.kr</t>
-        </is>
-      </c>
+          <t>balancelab_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1350-7099</t>
+          <t>0507-1368-9549</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄대로5길 21 2층 E203, E204호</t>
+          <t>경기도 화성시 병점구 병점노을4로 19 골든스퀘어원 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.physiostudio.co.kr/</t>
+          <t>https://www.instagram.com/balancefit_pt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="Q6" t="n">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="R6" t="n">
-        <v>280</v>
+        <v>217</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2075538417</t>
+          <t>2050262388</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075538417</t>
+          <t>https://m.place.naver.com/place/2050262388</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1038,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>비전휘트니스 동탄점</t>
+          <t>파워하우스짐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>visionfitness4@naver.com</t>
+          <t>powerhousegym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1352-4687</t>
+          <t>0507-1417-2272</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄중심상가2길 26-31 가희프라자 5층</t>
+          <t>경기도 화성시 동탄구 여울로 178-5 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://litt.ly/visionfitness4</t>
+          <t>http://pf.kakao.com/_xhSxoCG/chat</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,22 +1086,22 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2191</v>
+        <v>1664</v>
       </c>
       <c r="Q7" t="n">
-        <v>5108</v>
+        <v>647</v>
       </c>
       <c r="R7" t="n">
-        <v>7299</v>
+        <v>2311</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1525661824</t>
+          <t>1361155442</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1525661824</t>
+          <t>https://m.place.naver.com/place/1361155442</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1132,34 +1132,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>파워하우스짐</t>
+          <t>바이민짐 새솔점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>powerhousegym@naver.com</t>
+          <t>bymingym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1417-2272</t>
+          <t>0507-1474-0821</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 여울로 178-5 4층</t>
+          <t>경기도 화성시 만세구 수노을2로 7 메인프라자 1동 801호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhSxoCG/chat</t>
+          <t>https://www.instagram.com/bymingym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1180,22 +1180,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1660</v>
+        <v>1595</v>
       </c>
       <c r="Q8" t="n">
-        <v>647</v>
+        <v>999</v>
       </c>
       <c r="R8" t="n">
-        <v>2307</v>
+        <v>2594</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,51 +1204,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1361155442</t>
+          <t>1946317804</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1361155442</t>
+          <t>https://m.place.naver.com/place/1946317804</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>바이민짐 새솔점 헬스&amp;PT</t>
+          <t>어테인 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bymingym@naver.com</t>
+          <t>chlwlgns6849@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1474-0821</t>
+          <t>0507-1413-5543</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 화성시 만세구 수노을2로 7 메인프라자 1동 801호</t>
+          <t>경기도 화성시 효행구 봉담읍 상리3길 43-18 지음프라자2, 501호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bymingym</t>
+          <t>https://blog.naver.com/chlwlgns6849</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1590</v>
+        <v>126</v>
       </c>
       <c r="Q9" t="n">
-        <v>997</v>
+        <v>213</v>
       </c>
       <c r="R9" t="n">
-        <v>2587</v>
+        <v>339</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,51 +1298,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1946317804</t>
+          <t>1207439300</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1946317804</t>
+          <t>https://m.place.naver.com/place/1207439300</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>어테인 PT</t>
+          <t>파워맥스짐 헬스&amp;PT 병점본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>chlwlgns6849@naver.com</t>
+          <t>powermaxgym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1413-5543</t>
+          <t>0507-1394-6202</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 화성시 효행구 봉담읍 상리3길 43-18 지음프라자2, 501호</t>
+          <t>경기도 화성시 병점구 병점노을7로 5 603호~609호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chlwlgns6849</t>
+          <t>https://www.instagram.com/power_max_gym?igshid=OGQ5ZDc2ODk2ZA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>126</v>
+        <v>2690</v>
       </c>
       <c r="Q10" t="n">
-        <v>213</v>
+        <v>1025</v>
       </c>
       <c r="R10" t="n">
-        <v>339</v>
+        <v>3715</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,51 +1392,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1207439300</t>
+          <t>1941293926</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1207439300</t>
+          <t>https://m.place.naver.com/place/1941293926</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>파워맥스짐 헬스&amp;PT 병점본점</t>
+          <t>위더핏 PT 동탄목동점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>powermaxgym@naver.com</t>
+          <t>wethefit@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1394-6202</t>
+          <t>0507-1356-0494</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 화성시 병점구 병점노을7로 5 603호~609호</t>
+          <t>경기도 화성시 동탄구 동탄순환대로20길 124 우성스타파크A 609호 위더핏 PT 동탄목동점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/power_max_gym?igshid=OGQ5ZDc2ODk2ZA%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/wethefit</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2687</v>
+        <v>247</v>
       </c>
       <c r="Q11" t="n">
-        <v>1023</v>
+        <v>260</v>
       </c>
       <c r="R11" t="n">
-        <v>3710</v>
+        <v>507</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,17 +1486,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1941293926</t>
+          <t>1114041606</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1941293926</t>
+          <t>https://m.place.naver.com/place/1114041606</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/화성_PT.xlsx
+++ b/naver-place-crawler/results_health/화성_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -675,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄광역환승로 62 삼정그린코아시티 B1</t>
+          <t>경기 화성시 동탄구 동탄광역환승로 62 삼정그린코아시티 B1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vyv3</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -769,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 화성시 병점구 효행로 1073 거성프라자 9층</t>
+          <t>경기 화성시 병점구 효행로 1073 거성프라자 9층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +798,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41u1h</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -961,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 화성시 병점구 병점노을4로 19 골든스퀘어원 3층</t>
+          <t>경기 화성시 병점구 병점노을4로 19 골든스퀘어원 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -986,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wukj0vg</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1033,34 +1045,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>파워하우스짐</t>
+          <t>여성전용 올더핏 PT&amp;필라테스 병점동탄점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>powerhousegym@naver.com</t>
+          <t>allthefit_bj@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1417-2272</t>
+          <t>0507-1354-1478</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 여울로 178-5 4층</t>
+          <t>경기 화성시 병점구 병점노을4로 5 10층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhSxoCG/chat</t>
+          <t>http://pf.kakao.com/_giRiG</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1080,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wqf8</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>O</t>
@@ -1091,17 +1107,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1664</v>
+        <v>132</v>
       </c>
       <c r="Q7" t="n">
-        <v>647</v>
+        <v>547</v>
       </c>
       <c r="R7" t="n">
-        <v>2311</v>
+        <v>679</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1361155442</t>
+          <t>1442656447</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1361155442</t>
+          <t>https://m.place.naver.com/place/1442656447</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1132,34 +1148,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>바이민짐 새솔점 헬스&amp;PT</t>
+          <t>파워하우스짐</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bymingym@naver.com</t>
+          <t>powerhousegym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1474-0821</t>
+          <t>0507-1417-2272</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 화성시 만세구 수노을2로 7 메인프라자 1동 801호</t>
+          <t>경기 화성시 동탄구 여울로 178-5 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bymingym</t>
+          <t>http://pf.kakao.com/_xhSxoCG/chat</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1174,28 +1190,32 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wg22vle</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1595</v>
+        <v>1664</v>
       </c>
       <c r="Q8" t="n">
-        <v>999</v>
+        <v>647</v>
       </c>
       <c r="R8" t="n">
-        <v>2594</v>
+        <v>2311</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1946317804</t>
+          <t>1361155442</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1946317804</t>
+          <t>https://m.place.naver.com/place/1361155442</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1221,34 +1241,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>어테인 PT</t>
+          <t>바이민짐 새솔점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>chlwlgns6849@naver.com</t>
+          <t>bymingym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1413-5543</t>
+          <t>0507-1474-0821</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 화성시 효행구 봉담읍 상리3길 43-18 지음프라자2, 501호</t>
+          <t>경기 화성시 만세구 수노을2로 7 메인프라자 1동 801호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chlwlgns6849</t>
+          <t>https://www.instagram.com/bymingym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,15 +1283,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44nn7</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>126</v>
+        <v>1595</v>
       </c>
       <c r="Q9" t="n">
-        <v>213</v>
+        <v>999</v>
       </c>
       <c r="R9" t="n">
-        <v>339</v>
+        <v>2594</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1207439300</t>
+          <t>1946317804</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1207439300</t>
+          <t>https://m.place.naver.com/place/1946317804</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1315,34 +1339,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>파워맥스짐 헬스&amp;PT 병점본점</t>
+          <t>어테인 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>powermaxgym@naver.com</t>
+          <t>chlwlgns6849@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1394-6202</t>
+          <t>0507-1413-5543</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 화성시 병점구 병점노을7로 5 603호~609호</t>
+          <t>경기 화성시 효행구 봉담읍 상리3길 43-18 지음프라자2, 501호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/power_max_gym?igshid=OGQ5ZDc2ODk2ZA%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/chlwlgns6849</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1357,15 +1381,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wxqt8pa</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2690</v>
+        <v>126</v>
       </c>
       <c r="Q10" t="n">
-        <v>1025</v>
+        <v>213</v>
       </c>
       <c r="R10" t="n">
-        <v>3715</v>
+        <v>339</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1941293926</t>
+          <t>1207439300</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1941293926</t>
+          <t>https://m.place.naver.com/place/1207439300</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1409,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>위더핏 PT 동탄목동점</t>
+          <t>파워맥스짐 헬스&amp;PT 병점본점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wethefit@naver.com</t>
+          <t>powermaxgym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1356-0494</t>
+          <t>0507-1394-6202</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄순환대로20길 124 우성스타파크A 609호 위더핏 PT 동탄목동점</t>
+          <t>경기 화성시 병점구 병점노을7로 5 603호~609호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wethefit</t>
+          <t>https://www.instagram.com/power_max_gym?igshid=OGQ5ZDc2ODk2ZA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1451,15 +1479,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5t5oj</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1471,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>247</v>
+        <v>2690</v>
       </c>
       <c r="Q11" t="n">
-        <v>260</v>
+        <v>1026</v>
       </c>
       <c r="R11" t="n">
-        <v>507</v>
+        <v>3716</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1114041606</t>
+          <t>1941293926</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1114041606</t>
+          <t>https://m.place.naver.com/place/1941293926</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/화성_PT.xlsx
+++ b/naver-place-crawler/results_health/화성_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -624,10 +624,10 @@
         <v>1045</v>
       </c>
       <c r="Q2" t="n">
-        <v>6248</v>
+        <v>6249</v>
       </c>
       <c r="R2" t="n">
-        <v>7293</v>
+        <v>7294</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 화성시 동탄구 동탄광역환승로 62 삼정그린코아시티 B1</t>
+          <t>경기도 화성시 동탄구 동탄광역환승로 62 삼정그린코아시티 B1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -700,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5vyv3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -756,34 +752,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>병점 PT 케이토탈 헬스</t>
+          <t>피지오스튜디오 필라테스 &amp; PT 동탄호수공원점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>wjhk4@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>physiostudio2021@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>contact@physiostudio.co.kr</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>031-893-1005</t>
+          <t>0507-1350-7099</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 화성시 병점구 효행로 1073 거성프라자 9층</t>
+          <t>경기도 화성시 동탄구 동탄대로5길 21 2층 E203, E204호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wjhk4</t>
+          <t>https://www.physiostudio.co.kr/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -798,14 +798,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w41u1h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>707</v>
+        <v>77</v>
       </c>
       <c r="Q4" t="n">
-        <v>2025</v>
+        <v>207</v>
       </c>
       <c r="R4" t="n">
-        <v>2732</v>
+        <v>284</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>35111701</t>
+          <t>2075538417</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35111701</t>
+          <t>https://m.place.naver.com/place/2075538417</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,38 +850,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피지오스튜디오 필라테스 &amp; PT 동탄호수공원점</t>
+          <t>병점 PT 케이토탈 헬스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>physiostudio2021@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>contact@physiostudio.co.kr</t>
-        </is>
-      </c>
+          <t>wjhk4@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1350-7099</t>
+          <t>031-893-1005</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄대로5길 21 2층 E203, E204호</t>
+          <t>경기도 화성시 병점구 효행로 1073 거성프라자 9층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.physiostudio.co.kr/</t>
+          <t>https://blog.naver.com/wjhk4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -915,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>76</v>
+        <v>707</v>
       </c>
       <c r="Q5" t="n">
-        <v>207</v>
+        <v>2026</v>
       </c>
       <c r="R5" t="n">
-        <v>283</v>
+        <v>2733</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2075538417</t>
+          <t>35111701</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075538417</t>
+          <t>https://m.place.naver.com/place/35111701</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -952,34 +944,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>밸런스핏 PT&amp;헬스 동탄병점역점</t>
+          <t>프로핏97 PT 동탄1호점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>balancelab_pt@naver.com</t>
+          <t>ryn8118@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1368-9549</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 화성시 병점구 병점노을4로 19 골든스퀘어원 3층</t>
+          <t>경기도 화성시 동탄구 동탄기흥로520번나길 18 101호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/balancefit_pt</t>
+          <t>https://pf.kakao.com/_WaFeK</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -994,17 +982,13 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wukj0vg</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1013,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>27</v>
+        <v>649</v>
       </c>
       <c r="Q6" t="n">
-        <v>190</v>
+        <v>1907</v>
       </c>
       <c r="R6" t="n">
-        <v>217</v>
+        <v>2556</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2050262388</t>
+          <t>1299138186</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2050262388</t>
+          <t>https://m.place.naver.com/place/1299138186</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1067,7 +1051,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 화성시 병점구 병점노을4로 5 10층</t>
+          <t>경기도 화성시 병점구 병점노을4로 5 10층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1092,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wqf8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>O</t>
@@ -1114,10 +1094,10 @@
         <v>132</v>
       </c>
       <c r="Q7" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="R7" t="n">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1165,7 +1145,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 화성시 동탄구 여울로 178-5 4층</t>
+          <t>경기도 화성시 동탄구 여울로 178-5 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1190,14 +1170,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wg22vle</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>O</t>
@@ -1263,7 +1239,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 화성시 만세구 수노을2로 7 메인프라자 1동 801호</t>
+          <t>경기도 화성시 만세구 수노을2로 7 메인프라자 1동 801호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1288,14 +1264,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w44nn7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1361,7 +1333,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 화성시 효행구 봉담읍 상리3길 43-18 지음프라자2, 501호</t>
+          <t>경기도 화성시 효행구 봉담읍 상리3길 43-18 지음프라자2, 501호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1386,14 +1358,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wxqt8pa</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1459,7 +1427,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 화성시 병점구 병점노을7로 5 603호~609호</t>
+          <t>경기도 화성시 병점구 병점노을7로 5 603호~609호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1484,14 +1452,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5t5oj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1503,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2690</v>
+        <v>2693</v>
       </c>
       <c r="Q11" t="n">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="R11" t="n">
-        <v>3716</v>
+        <v>3720</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/화성_PT.xlsx
+++ b/naver-place-crawler/results_health/화성_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -624,10 +624,10 @@
         <v>1045</v>
       </c>
       <c r="Q2" t="n">
-        <v>6249</v>
+        <v>6259</v>
       </c>
       <c r="R2" t="n">
-        <v>7294</v>
+        <v>7304</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1029,39 +1029,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>여성전용 올더핏 PT&amp;필라테스 병점동탄점</t>
+          <t>바이민짐 새솔점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>allthefit_bj@naver.com</t>
+          <t>bymingym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1354-1478</t>
+          <t>0507-1474-0821</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 화성시 병점구 병점노을4로 5 10층</t>
+          <t>경기도 화성시 만세구 수노을2로 7 메인프라자 1동 801호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_giRiG</t>
+          <t>https://www.instagram.com/bymingym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>132</v>
+        <v>1596</v>
       </c>
       <c r="Q7" t="n">
-        <v>550</v>
+        <v>999</v>
       </c>
       <c r="R7" t="n">
-        <v>682</v>
+        <v>2595</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1442656447</t>
+          <t>1946317804</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1442656447</t>
+          <t>https://m.place.naver.com/place/1946317804</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,39 +1123,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>파워하우스짐</t>
+          <t>어테인 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>powerhousegym@naver.com</t>
+          <t>chlwlgns6849@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1417-2272</t>
+          <t>0507-1413-5543</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 여울로 178-5 4층</t>
+          <t>경기도 화성시 효행구 봉담읍 상리3길 43-18 지음프라자2, 501호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhSxoCG/chat</t>
+          <t>https://blog.naver.com/chlwlgns6849</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1176,22 +1176,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1664</v>
+        <v>126</v>
       </c>
       <c r="Q8" t="n">
-        <v>647</v>
+        <v>213</v>
       </c>
       <c r="R8" t="n">
-        <v>2311</v>
+        <v>339</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1361155442</t>
+          <t>1207439300</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1361155442</t>
+          <t>https://m.place.naver.com/place/1207439300</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1222,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>바이민짐 새솔점 헬스&amp;PT</t>
+          <t>파워맥스짐 헬스&amp;PT 병점본점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bymingym@naver.com</t>
+          <t>powermaxgym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1474-0821</t>
+          <t>0507-1394-6202</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 화성시 만세구 수노을2로 7 메인프라자 1동 801호</t>
+          <t>경기도 화성시 병점구 병점노을7로 5 603호~609호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bymingym</t>
+          <t>https://www.instagram.com/power_max_gym?igshid=OGQ5ZDc2ODk2ZA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1595</v>
+        <v>2694</v>
       </c>
       <c r="Q9" t="n">
-        <v>999</v>
+        <v>1029</v>
       </c>
       <c r="R9" t="n">
-        <v>2594</v>
+        <v>3723</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1946317804</t>
+          <t>1941293926</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1946317804</t>
+          <t>https://m.place.naver.com/place/1941293926</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1316,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>어테인 PT</t>
+          <t>위더핏 PT 동탄목동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>chlwlgns6849@naver.com</t>
+          <t>wethefit@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1413-5543</t>
+          <t>0507-1356-0494</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 화성시 효행구 봉담읍 상리3길 43-18 지음프라자2, 501호</t>
+          <t>경기도 화성시 동탄구 동탄순환대로20길 124 우성스타파크A 609호 위더핏 PT 동탄목동점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chlwlgns6849</t>
+          <t>https://blog.naver.com/wethefit</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>126</v>
+        <v>247</v>
       </c>
       <c r="Q10" t="n">
-        <v>213</v>
+        <v>260</v>
       </c>
       <c r="R10" t="n">
-        <v>339</v>
+        <v>507</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,109 +1388,15 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1207439300</t>
+          <t>1114041606</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1207439300</t>
+          <t>https://m.place.naver.com/place/1114041606</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>파워맥스짐 헬스&amp;PT 병점본점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>powermaxgym@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1394-6202</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>경기도 화성시 병점구 병점노을7로 5 603호~609호</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/power_max_gym?igshid=OGQ5ZDc2ODk2ZA%3D%3D&amp;utm_source=qr</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>2693</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1027</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3720</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1941293926</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1941293926</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/화성_PT.xlsx
+++ b/naver-place-crawler/results_health/화성_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,34 +564,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>비전휘트니스 동탄역점</t>
+          <t>도라PT앤 동탄점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>visionfitness10@naver.com</t>
+          <t>dora_pt-jack_dive@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1348-9691</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄대로19길 10 신유메디프라자 8층</t>
+          <t>경기도 화성시 동탄구 동탄대로 446 그란비아스타 5층 5107호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://litt.ly/visionfitness1001</t>
+          <t>https://blog.naver.com/dora_pt-jack_dive</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,7 +608,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1045</v>
+        <v>37</v>
       </c>
       <c r="Q2" t="n">
-        <v>6259</v>
+        <v>80</v>
       </c>
       <c r="R2" t="n">
-        <v>7304</v>
+        <v>117</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +632,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>87233617</t>
+          <t>1662485862</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/87233617</t>
+          <t>https://m.place.naver.com/place/1662485862</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>모델짐 헬스 PT 스피닝 여울공원점</t>
+          <t>피트니스M 헬스&amp;PT 봉담</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>modelgym_dongtan@naver.com</t>
+          <t>fitness0221@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1366-2845</t>
+          <t>0507-1355-4598</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄광역환승로 62 삼정그린코아시티 B1</t>
+          <t>경기도 화성시 효행구 봉담읍 상봉길 31 3층 304호, 305호, 306호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.modelgym.co.kr</t>
+          <t>https://pf.kakao.com/_ximHWn</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,12 +686,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -706,7 +702,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>225</v>
+        <v>447</v>
       </c>
       <c r="Q3" t="n">
-        <v>3192</v>
+        <v>685</v>
       </c>
       <c r="R3" t="n">
-        <v>3417</v>
+        <v>1132</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1218747362</t>
+          <t>1836647807</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1218747362</t>
+          <t>https://m.place.naver.com/place/1836647807</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -752,33 +748,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피지오스튜디오 필라테스 &amp; PT 동탄호수공원점</t>
+          <t>비전휘트니스 동탄역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>physiostudio2021@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>contact@physiostudio.co.kr</t>
-        </is>
-      </c>
+          <t>visionfitness10@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1350-7099</t>
+          <t>0507-1348-9691</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄대로5길 21 2층 E203, E204호</t>
+          <t>경기도 화성시 동탄구 동탄대로19길 10 신유메디프라자 8층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.physiostudio.co.kr/</t>
+          <t>https://litt.ly/visionfitness1001</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +785,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -813,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>77</v>
+        <v>1045</v>
       </c>
       <c r="Q4" t="n">
-        <v>207</v>
+        <v>6265</v>
       </c>
       <c r="R4" t="n">
-        <v>284</v>
+        <v>7310</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2075538417</t>
+          <t>87233617</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075538417</t>
+          <t>https://m.place.naver.com/place/87233617</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -850,39 +842,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>병점 PT 케이토탈 헬스</t>
+          <t>모델짐 헬스 PT 스피닝 여울공원점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>wjhk4@naver.com</t>
+          <t>modelgym_dongtan@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>031-893-1005</t>
+          <t>0507-1366-2845</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 화성시 병점구 효행로 1073 거성프라자 9층</t>
+          <t>경기도 화성시 동탄구 동탄광역환승로 62 삼정그린코아시티 B1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wjhk4</t>
+          <t>https://www.modelgym.co.kr</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -907,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>707</v>
+        <v>225</v>
       </c>
       <c r="Q5" t="n">
-        <v>2026</v>
+        <v>3192</v>
       </c>
       <c r="R5" t="n">
-        <v>2733</v>
+        <v>3417</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>35111701</t>
+          <t>1218747362</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35111701</t>
+          <t>https://m.place.naver.com/place/1218747362</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -944,25 +936,33 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>프로핏97 PT 동탄1호점</t>
+          <t>피지오스튜디오 필라테스 &amp; PT 동탄호수공원점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ryn8118@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>physiostudio2021@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>contact@physiostudio.co.kr</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1350-7099</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄기흥로520번나길 18 101호</t>
+          <t>경기도 화성시 동탄구 동탄대로5길 21 2층 E203, E204호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_WaFeK</t>
+          <t>https://www.physiostudio.co.kr/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>649</v>
+        <v>77</v>
       </c>
       <c r="Q6" t="n">
-        <v>1907</v>
+        <v>207</v>
       </c>
       <c r="R6" t="n">
-        <v>2556</v>
+        <v>284</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1012,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1299138186</t>
+          <t>2075538417</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1299138186</t>
+          <t>https://m.place.naver.com/place/2075538417</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>바이민짐 새솔점 헬스&amp;PT</t>
+          <t>병점 PT 케이토탈 헬스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bymingym@naver.com</t>
+          <t>wjhk4@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1474-0821</t>
+          <t>031-893-1005</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 화성시 만세구 수노을2로 7 메인프라자 1동 801호</t>
+          <t>경기도 화성시 병점구 효행로 1073 거성프라자 9층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bymingym</t>
+          <t>https://blog.naver.com/wjhk4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1596</v>
+        <v>707</v>
       </c>
       <c r="Q7" t="n">
-        <v>999</v>
+        <v>2026</v>
       </c>
       <c r="R7" t="n">
-        <v>2595</v>
+        <v>2733</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1946317804</t>
+          <t>35111701</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1946317804</t>
+          <t>https://m.place.naver.com/place/35111701</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1128,34 +1128,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>어테인 PT</t>
+          <t>프로핏97 PT 동탄1호점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>chlwlgns6849@naver.com</t>
+          <t>ryn8118@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1413-5543</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 화성시 효행구 봉담읍 상리3길 43-18 지음프라자2, 501호</t>
+          <t>경기도 화성시 동탄구 동탄기흥로520번나길 18 101호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chlwlgns6849</t>
+          <t>https://pf.kakao.com/_WaFeK</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,7 +1161,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1176,7 +1172,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>126</v>
+        <v>649</v>
       </c>
       <c r="Q8" t="n">
-        <v>213</v>
+        <v>1907</v>
       </c>
       <c r="R8" t="n">
-        <v>339</v>
+        <v>2556</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1207439300</t>
+          <t>1299138186</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1207439300</t>
+          <t>https://m.place.naver.com/place/1299138186</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1222,34 +1218,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>파워맥스짐 헬스&amp;PT 병점본점</t>
+          <t>파워하우스짐</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>powermaxgym@naver.com</t>
+          <t>powerhousegym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1394-6202</t>
+          <t>0507-1417-2272</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 화성시 병점구 병점노을7로 5 603호~609호</t>
+          <t>경기도 화성시 동탄구 여울로 178-5 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/power_max_gym?igshid=OGQ5ZDc2ODk2ZA%3D%3D&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_xhSxoCG/chat</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1270,22 +1266,22 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2694</v>
+        <v>1665</v>
       </c>
       <c r="Q9" t="n">
-        <v>1029</v>
+        <v>647</v>
       </c>
       <c r="R9" t="n">
-        <v>3723</v>
+        <v>2312</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1290,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1941293926</t>
+          <t>1361155442</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1941293926</t>
+          <t>https://m.place.naver.com/place/1361155442</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>위더핏 PT 동탄목동점</t>
+          <t>바이민짐 새솔점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wethefit@naver.com</t>
+          <t>bymingym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1356-0494</t>
+          <t>0507-1474-0821</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄순환대로20길 124 우성스타파크A 609호 위더핏 PT 동탄목동점</t>
+          <t>경기도 화성시 만세구 수노을2로 7 메인프라자 1동 801호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wethefit</t>
+          <t>https://www.instagram.com/bymingym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1349,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>247</v>
+        <v>1596</v>
       </c>
       <c r="Q10" t="n">
-        <v>260</v>
+        <v>999</v>
       </c>
       <c r="R10" t="n">
-        <v>507</v>
+        <v>2595</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1384,205 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1114041606</t>
+          <t>1946317804</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1114041606</t>
+          <t>https://m.place.naver.com/place/1946317804</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>어테인 PT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>chlwlgns6849@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1413-5543</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>경기도 화성시 효행구 봉담읍 상리3길 43-18 지음프라자2, 501호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/chlwlgns6849</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>213</v>
+      </c>
+      <c r="R11" t="n">
+        <v>339</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1207439300</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1207439300</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>파워맥스짐 헬스&amp;PT 병점본점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>powermaxgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1394-6202</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 화성시 병점구 병점노을7로 5 603호~609호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/power_max_gym?igshid=OGQ5ZDc2ODk2ZA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>2695</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1030</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3725</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1941293926</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1941293926</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/화성_PT.xlsx
+++ b/naver-place-crawler/results_health/화성_PT.xlsx
@@ -426,7 +426,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -654,29 +654,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피트니스M 헬스&amp;PT 봉담</t>
+          <t>더제이피트니스 향남1지구점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fitness0221@naver.com</t>
+          <t>thejfitness03@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1355-4598</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 화성시 효행구 봉담읍 상봉길 31 3층 304호, 305호, 306호</t>
+          <t>경기도 화성시 만세구 향남읍 행정중앙2로 63-34 3층 더제이피트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_ximHWn</t>
+          <t>https://booking.naver.com/booking/6/bizes/706808</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -686,12 +682,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -702,7 +698,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -711,13 +707,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>447</v>
+        <v>1176</v>
       </c>
       <c r="Q3" t="n">
-        <v>685</v>
+        <v>450</v>
       </c>
       <c r="R3" t="n">
-        <v>1132</v>
+        <v>1626</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,12 +722,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1836647807</t>
+          <t>1417520820</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1836647807</t>
+          <t>https://m.place.naver.com/place/1417520820</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -808,10 +804,10 @@
         <v>1045</v>
       </c>
       <c r="Q4" t="n">
-        <v>6265</v>
+        <v>6270</v>
       </c>
       <c r="R4" t="n">
-        <v>7310</v>
+        <v>7315</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1094,10 +1090,10 @@
         <v>707</v>
       </c>
       <c r="Q7" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="R7" t="n">
-        <v>2733</v>
+        <v>2735</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1184,10 +1180,10 @@
         <v>649</v>
       </c>
       <c r="Q8" t="n">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="R8" t="n">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1218,29 +1214,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>파워하우스짐</t>
+          <t>비전휘트니스 동탄점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>powerhousegym@naver.com</t>
+          <t>visionfitness4@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1417-2272</t>
+          <t>0507-1352-4687</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 여울로 178-5 4층</t>
+          <t>경기도 화성시 동탄구 동탄중심상가2길 26-31 가희프라자 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhSxoCG/chat</t>
+          <t>https://litt.ly/visionfitness4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1266,22 +1262,22 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1665</v>
+        <v>2191</v>
       </c>
       <c r="Q9" t="n">
-        <v>647</v>
+        <v>5123</v>
       </c>
       <c r="R9" t="n">
-        <v>2312</v>
+        <v>7314</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1286,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1361155442</t>
+          <t>1525661824</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1361155442</t>
+          <t>https://m.place.naver.com/place/1525661824</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1312,34 +1308,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>바이민짐 새솔점 헬스&amp;PT</t>
+          <t>파워하우스짐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bymingym@naver.com</t>
+          <t>powerhousegym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1474-0821</t>
+          <t>0507-1417-2272</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 화성시 만세구 수노을2로 7 메인프라자 1동 801호</t>
+          <t>경기도 화성시 동탄구 여울로 178-5 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bymingym</t>
+          <t>http://pf.kakao.com/_xhSxoCG/chat</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1360,22 +1356,22 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1596</v>
+        <v>1665</v>
       </c>
       <c r="Q10" t="n">
-        <v>999</v>
+        <v>647</v>
       </c>
       <c r="R10" t="n">
-        <v>2595</v>
+        <v>2312</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,12 +1380,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1946317804</t>
+          <t>1361155442</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1946317804</t>
+          <t>https://m.place.naver.com/place/1361155442</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1401,34 +1397,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>어테인 PT</t>
+          <t>바이민짐 새솔점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>chlwlgns6849@naver.com</t>
+          <t>bymingym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1413-5543</t>
+          <t>0507-1474-0821</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 화성시 효행구 봉담읍 상리3길 43-18 지음프라자2, 501호</t>
+          <t>경기도 화성시 만세구 수노을2로 7 메인프라자 1동 801호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chlwlgns6849</t>
+          <t>https://www.instagram.com/bymingym</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1443,7 +1439,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1463,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>126</v>
+        <v>1596</v>
       </c>
       <c r="Q11" t="n">
-        <v>213</v>
+        <v>999</v>
       </c>
       <c r="R11" t="n">
-        <v>339</v>
+        <v>2595</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,12 +1474,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1207439300</t>
+          <t>1946317804</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1207439300</t>
+          <t>https://m.place.naver.com/place/1946317804</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1495,34 +1491,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>파워맥스짐 헬스&amp;PT 병점본점</t>
+          <t>어테인 PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>powermaxgym@naver.com</t>
+          <t>chlwlgns6849@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1394-6202</t>
+          <t>0507-1413-5543</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 화성시 병점구 병점노을7로 5 603호~609호</t>
+          <t>경기도 화성시 효행구 봉담읍 상리3길 43-18 지음프라자2, 501호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/power_max_gym?igshid=OGQ5ZDc2ODk2ZA%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/chlwlgns6849</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1537,7 +1533,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1557,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2695</v>
+        <v>126</v>
       </c>
       <c r="Q12" t="n">
-        <v>1030</v>
+        <v>213</v>
       </c>
       <c r="R12" t="n">
-        <v>3725</v>
+        <v>339</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,12 +1568,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1941293926</t>
+          <t>1207439300</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1941293926</t>
+          <t>https://m.place.naver.com/place/1207439300</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/화성_PT.xlsx
+++ b/naver-place-crawler/results_health/화성_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -620,10 +620,10 @@
         <v>37</v>
       </c>
       <c r="Q2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -804,10 +804,10 @@
         <v>1045</v>
       </c>
       <c r="Q4" t="n">
-        <v>6270</v>
+        <v>6277</v>
       </c>
       <c r="R4" t="n">
-        <v>7315</v>
+        <v>7322</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -838,29 +838,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>모델짐 헬스 PT 스피닝 여울공원점</t>
+          <t>피지오스튜디오 필라테스 &amp; PT 동탄호수공원점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>modelgym_dongtan@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>physiostudio2021@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>contact@physiostudio.co.kr</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1366-2845</t>
+          <t>0507-1350-7099</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄광역환승로 62 삼정그린코아시티 B1</t>
+          <t>경기도 화성시 동탄구 동탄대로5길 21 2층 E203, E204호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.modelgym.co.kr</t>
+          <t>https://www.physiostudio.co.kr/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -870,7 +874,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -895,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>225</v>
+        <v>77</v>
       </c>
       <c r="Q5" t="n">
-        <v>3192</v>
+        <v>207</v>
       </c>
       <c r="R5" t="n">
-        <v>3417</v>
+        <v>284</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,12 +914,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1218747362</t>
+          <t>2075538417</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1218747362</t>
+          <t>https://m.place.naver.com/place/2075538417</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -932,33 +936,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피지오스튜디오 필라테스 &amp; PT 동탄호수공원점</t>
+          <t>모델짐 헬스 PT 스피닝 여울공원점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>physiostudio2021@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>contact@physiostudio.co.kr</t>
-        </is>
-      </c>
+          <t>modelgym_dongtan@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1350-7099</t>
+          <t>0507-1366-2845</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄대로5길 21 2층 E203, E204호</t>
+          <t>경기도 화성시 동탄구 동탄광역환승로 62 삼정그린코아시티 B1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.physiostudio.co.kr/</t>
+          <t>https://www.modelgym.co.kr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>77</v>
+        <v>225</v>
       </c>
       <c r="Q6" t="n">
-        <v>207</v>
+        <v>3193</v>
       </c>
       <c r="R6" t="n">
-        <v>284</v>
+        <v>3418</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2075538417</t>
+          <t>1218747362</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075538417</t>
+          <t>https://m.place.naver.com/place/1218747362</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1124,30 +1124,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>프로핏97 PT 동탄1호점</t>
+          <t>트렌드짐</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ryn8118@naver.com</t>
+          <t>trendgym2024@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1366-0903</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄기흥로520번나길 18 101호</t>
+          <t>경기도 화성시 병점구 장조2로 29 도담스퀘어 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_WaFeK</t>
+          <t>https://blog.naver.com/trendgym2024</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1157,7 +1161,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1168,7 +1172,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1177,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>649</v>
+        <v>323</v>
       </c>
       <c r="Q8" t="n">
-        <v>1908</v>
+        <v>291</v>
       </c>
       <c r="R8" t="n">
-        <v>2557</v>
+        <v>614</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1299138186</t>
+          <t>1527157868</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1299138186</t>
+          <t>https://m.place.naver.com/place/1527157868</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1214,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비전휘트니스 동탄점</t>
+          <t>파워하우스짐</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>visionfitness4@naver.com</t>
+          <t>powerhousegym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1352-4687</t>
+          <t>0507-1417-2272</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄중심상가2길 26-31 가희프라자 5층</t>
+          <t>경기도 화성시 동탄구 여울로 178-5 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://litt.ly/visionfitness4</t>
+          <t>http://pf.kakao.com/_xhSxoCG/chat</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1262,22 +1266,22 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2191</v>
+        <v>1665</v>
       </c>
       <c r="Q9" t="n">
-        <v>5123</v>
+        <v>647</v>
       </c>
       <c r="R9" t="n">
-        <v>7314</v>
+        <v>2312</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1525661824</t>
+          <t>1361155442</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1525661824</t>
+          <t>https://m.place.naver.com/place/1361155442</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1308,34 +1312,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>파워하우스짐</t>
+          <t>바이민짐 새솔점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>powerhousegym@naver.com</t>
+          <t>bymingym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1417-2272</t>
+          <t>0507-1474-0821</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 여울로 178-5 4층</t>
+          <t>경기도 화성시 만세구 수노을2로 7 메인프라자 1동 801호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhSxoCG/chat</t>
+          <t>https://www.instagram.com/bymingym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1356,22 +1360,22 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1665</v>
+        <v>1597</v>
       </c>
       <c r="Q10" t="n">
-        <v>647</v>
+        <v>999</v>
       </c>
       <c r="R10" t="n">
-        <v>2312</v>
+        <v>2596</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,12 +1384,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1361155442</t>
+          <t>1946317804</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1361155442</t>
+          <t>https://m.place.naver.com/place/1946317804</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1397,34 +1401,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>바이민짐 새솔점 헬스&amp;PT</t>
+          <t>어테인 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bymingym@naver.com</t>
+          <t>chlwlgns6849@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1474-0821</t>
+          <t>0507-1413-5543</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 화성시 만세구 수노을2로 7 메인프라자 1동 801호</t>
+          <t>경기도 화성시 효행구 봉담읍 상리3길 43-18 지음프라자2, 501호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bymingym</t>
+          <t>https://blog.naver.com/chlwlgns6849</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1439,7 +1443,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1459,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1596</v>
+        <v>126</v>
       </c>
       <c r="Q11" t="n">
-        <v>999</v>
+        <v>213</v>
       </c>
       <c r="R11" t="n">
-        <v>2595</v>
+        <v>339</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,109 +1478,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1946317804</t>
+          <t>1207439300</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1946317804</t>
+          <t>https://m.place.naver.com/place/1207439300</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>어테인 PT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>chlwlgns6849@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1413-5543</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기도 화성시 효행구 봉담읍 상리3길 43-18 지음프라자2, 501호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/chlwlgns6849</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>126</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>213</v>
-      </c>
-      <c r="R12" t="n">
-        <v>339</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1207439300</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1207439300</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/화성_PT.xlsx
+++ b/naver-place-crawler/results_health/화성_PT.xlsx
@@ -426,7 +426,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -642,7 +642,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -654,25 +654,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>더제이피트니스 향남1지구점</t>
+          <t>피트니스M 헬스&amp;PT 봉담</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>thejfitness03@naver.com</t>
+          <t>fitness0221@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1355-4598</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 화성시 만세구 향남읍 행정중앙2로 63-34 3층 더제이피트니스</t>
+          <t>경기도 화성시 효행구 봉담읍 상봉길 31 3층 304호, 305호, 306호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/706808</t>
+          <t>https://pf.kakao.com/_ximHWn</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -682,12 +686,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -698,7 +702,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -707,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1176</v>
+        <v>447</v>
       </c>
       <c r="Q3" t="n">
-        <v>450</v>
+        <v>686</v>
       </c>
       <c r="R3" t="n">
-        <v>1626</v>
+        <v>1133</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -722,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1417520820</t>
+          <t>1836647807</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1417520820</t>
+          <t>https://m.place.naver.com/place/1836647807</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -804,10 +808,10 @@
         <v>1045</v>
       </c>
       <c r="Q4" t="n">
-        <v>6277</v>
+        <v>6279</v>
       </c>
       <c r="R4" t="n">
-        <v>7322</v>
+        <v>7324</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -826,7 +830,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -924,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -963,7 +967,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1018,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1116,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1210,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1218,34 +1222,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>파워하우스짐</t>
+          <t>바이민짐 새솔점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>powerhousegym@naver.com</t>
+          <t>bymingym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1417-2272</t>
+          <t>0507-1474-0821</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 여울로 178-5 4층</t>
+          <t>경기도 화성시 만세구 수노을2로 7 메인프라자 1동 801호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhSxoCG/chat</t>
+          <t>https://www.instagram.com/bymingym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1266,22 +1270,22 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1665</v>
+        <v>1597</v>
       </c>
       <c r="Q9" t="n">
-        <v>647</v>
+        <v>999</v>
       </c>
       <c r="R9" t="n">
-        <v>2312</v>
+        <v>2596</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,51 +1294,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1361155442</t>
+          <t>1946317804</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1361155442</t>
+          <t>https://m.place.naver.com/place/1946317804</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>바이민짐 새솔점 헬스&amp;PT</t>
+          <t>어테인 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bymingym@naver.com</t>
+          <t>chlwlgns6849@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1474-0821</t>
+          <t>0507-1413-5543</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 화성시 만세구 수노을2로 7 메인프라자 1동 801호</t>
+          <t>경기도 화성시 효행구 봉담읍 상리3길 43-18 지음프라자2, 501호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bymingym</t>
+          <t>https://blog.naver.com/chlwlgns6849</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1349,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1597</v>
+        <v>126</v>
       </c>
       <c r="Q10" t="n">
-        <v>999</v>
+        <v>213</v>
       </c>
       <c r="R10" t="n">
-        <v>2596</v>
+        <v>339</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,51 +1388,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1946317804</t>
+          <t>1207439300</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1946317804</t>
+          <t>https://m.place.naver.com/place/1207439300</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>어테인 PT</t>
+          <t>파워맥스짐 헬스&amp;PT 병점본점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>chlwlgns6849@naver.com</t>
+          <t>powermaxgym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1413-5543</t>
+          <t>0507-1394-6202</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 화성시 효행구 봉담읍 상리3길 43-18 지음프라자2, 501호</t>
+          <t>경기도 화성시 병점구 병점노을7로 5 603호~609호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chlwlgns6849</t>
+          <t>https://www.instagram.com/power_max_gym?igshid=OGQ5ZDc2ODk2ZA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1443,7 +1447,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1463,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>126</v>
+        <v>2697</v>
       </c>
       <c r="Q11" t="n">
-        <v>213</v>
+        <v>1033</v>
       </c>
       <c r="R11" t="n">
-        <v>339</v>
+        <v>3730</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1207439300</t>
+          <t>1941293926</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1207439300</t>
+          <t>https://m.place.naver.com/place/1941293926</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/화성_PT.xlsx
+++ b/naver-place-crawler/results_health/화성_PT.xlsx
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -582,7 +582,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dora_pt-jack_dive</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -592,20 +592,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzjerw1</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -659,7 +663,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fitness0221@naver.com</t>
+          <t>fitnessm_3@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -676,17 +680,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_ximHWn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -696,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w587eza</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>O</t>
@@ -711,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Q3" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="R3" t="n">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -790,10 +798,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wfi2rb0</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -808,10 +820,10 @@
         <v>1045</v>
       </c>
       <c r="Q4" t="n">
-        <v>6279</v>
+        <v>6290</v>
       </c>
       <c r="R4" t="n">
-        <v>7324</v>
+        <v>7335</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -967,7 +979,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -982,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vyv3</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1056,7 +1072,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wjhk4</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,20 +1082,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41u1h</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1094,10 +1114,10 @@
         <v>707</v>
       </c>
       <c r="Q7" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="R7" t="n">
-        <v>2735</v>
+        <v>2736</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1150,7 +1170,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trendgym2024</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1160,20 +1180,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ir1x</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1227,7 +1251,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bymingym@naver.com</t>
+          <t>firstfitness_@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1244,7 +1268,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bymingym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,7 +1278,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1264,10 +1288,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44nn7</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="Q9" t="n">
         <v>999</v>
       </c>
       <c r="R9" t="n">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1321,7 +1349,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>chlwlgns6849@naver.com</t>
+          <t>attainpt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1338,7 +1366,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chlwlgns6849</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,20 +1376,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wxqt8pa</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1376,10 +1408,10 @@
         <v>126</v>
       </c>
       <c r="Q10" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R10" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1432,7 +1464,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/power_max_gym?igshid=OGQ5ZDc2ODk2ZA%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1442,7 +1474,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1452,10 +1484,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5t5oj</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>

--- a/naver-place-crawler/results_health/화성_PT.xlsx
+++ b/naver-place-crawler/results_health/화성_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,25 +559,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>도라PT앤 동탄점</t>
+          <t>피트니스M 헬스&amp;PT 봉담</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dora_pt-jack_dive@naver.com</t>
+          <t>fitnessm_3@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0507-1355-4598</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄대로 446 그란비아스타 5층 5107호</t>
+          <t>경기도 화성시 효행구 봉담읍 상봉길 31 3층 304호, 305호, 306호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -607,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wzjerw1</t>
+          <t>https://talk.naver.com/ct/w587eza</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>37</v>
+        <v>449</v>
       </c>
       <c r="Q2" t="n">
-        <v>81</v>
+        <v>687</v>
       </c>
       <c r="R2" t="n">
-        <v>118</v>
+        <v>1136</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,61 +640,61 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1662485862</t>
+          <t>1836647807</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1662485862</t>
+          <t>https://m.place.naver.com/place/1836647807</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피트니스M 헬스&amp;PT 봉담</t>
+          <t>비전휘트니스 동탄역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fitnessm_3@naver.com</t>
+          <t>visionfitness10@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1355-4598</t>
+          <t>0507-1348-9691</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 화성시 효행구 봉담읍 상봉길 31 3층 304호, 305호, 306호</t>
+          <t>경기도 화성시 동탄구 동탄대로19길 10 신유메디프라자 8층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://litt.ly/visionfitness1001</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -705,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w587eza</t>
+          <t>https://talk.naver.com/ct/wfi2rb0</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>449</v>
+        <v>1046</v>
       </c>
       <c r="Q3" t="n">
-        <v>687</v>
+        <v>6289</v>
       </c>
       <c r="R3" t="n">
-        <v>1136</v>
+        <v>7335</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1836647807</t>
+          <t>87233617</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1836647807</t>
+          <t>https://m.place.naver.com/place/87233617</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -756,29 +760,33 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>비전휘트니스 동탄역점</t>
+          <t>피지오스튜디오 필라테스 &amp; PT 동탄호수공원점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>visionfitness10@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>physiostudio2021@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>contact@physiostudio.co.kr</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1348-9691</t>
+          <t>0507-1350-7099</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄대로19길 10 신유메디프라자 8층</t>
+          <t>경기도 화성시 동탄구 동탄대로5길 21 2층 E203, E204호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://litt.ly/visionfitness1001</t>
+          <t>https://www.physiostudio.co.kr/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +801,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -803,7 +811,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wfi2rb0</t>
+          <t>https://talk.naver.com/ct/wgpx92l</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +825,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1045</v>
+        <v>77</v>
       </c>
       <c r="Q4" t="n">
-        <v>6290</v>
+        <v>207</v>
       </c>
       <c r="R4" t="n">
-        <v>7335</v>
+        <v>284</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +840,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>87233617</t>
+          <t>2075538417</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/87233617</t>
+          <t>https://m.place.naver.com/place/2075538417</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -854,43 +862,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피지오스튜디오 필라테스 &amp; PT 동탄호수공원점</t>
+          <t>모델짐 헬스 PT 스피닝 여울공원점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>physiostudio2021@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>contact@physiostudio.co.kr</t>
-        </is>
-      </c>
+          <t>modelgym_dongtan@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1350-7099</t>
+          <t>0507-1366-2845</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄대로5길 21 2층 E203, E204호</t>
+          <t>경기도 화성시 동탄구 동탄광역환승로 62 삼정그린코아시티 B1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.physiostudio.co.kr/</t>
+          <t>https://www.modelgym.co.kr</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -900,10 +904,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vyv3</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,13 +923,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>77</v>
+        <v>225</v>
       </c>
       <c r="Q5" t="n">
-        <v>207</v>
+        <v>3193</v>
       </c>
       <c r="R5" t="n">
-        <v>284</v>
+        <v>3418</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +938,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2075538417</t>
+          <t>1218747362</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075538417</t>
+          <t>https://m.place.naver.com/place/1218747362</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -952,34 +960,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>모델짐 헬스 PT 스피닝 여울공원점</t>
+          <t>병점 PT 케이토탈 헬스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>modelgym_dongtan@naver.com</t>
+          <t>wjhk4@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1366-2845</t>
+          <t>031-893-1005</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄광역환승로 62 삼정그린코아시티 B1</t>
+          <t>경기도 화성시 병점구 효행로 1073 거성프라자 9층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.modelgym.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -989,7 +997,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -999,7 +1007,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vyv3</t>
+          <t>https://talk.naver.com/ct/w41u1h</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1021,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>225</v>
+        <v>707</v>
       </c>
       <c r="Q6" t="n">
-        <v>3193</v>
+        <v>2029</v>
       </c>
       <c r="R6" t="n">
-        <v>3418</v>
+        <v>2736</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1036,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1218747362</t>
+          <t>35111701</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1218747362</t>
+          <t>https://m.place.naver.com/place/35111701</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1058,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>병점 PT 케이토탈 헬스</t>
+          <t>트렌드짐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>wjhk4@naver.com</t>
+          <t>trendgym2024@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>031-893-1005</t>
+          <t>0507-1366-0903</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 화성시 병점구 효행로 1073 거성프라자 9층</t>
+          <t>경기도 화성시 병점구 장조2로 29 도담스퀘어 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/trendgym2024</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,24 +1090,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w41u1h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>707</v>
+        <v>323</v>
       </c>
       <c r="Q7" t="n">
-        <v>2029</v>
+        <v>291</v>
       </c>
       <c r="R7" t="n">
-        <v>2736</v>
+        <v>614</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>35111701</t>
+          <t>1527157868</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35111701</t>
+          <t>https://m.place.naver.com/place/1527157868</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1148,24 +1152,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>트렌드짐</t>
+          <t>여성전용 올더핏 PT&amp;필라테스 병점동탄점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>trendgym2024@naver.com</t>
+          <t>allthefit@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1366-0903</t>
+          <t>0507-1354-1478</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 화성시 병점구 장조2로 29 도담스퀘어 3층</t>
+          <t>경기도 화성시 병점구 병점노을4로 5 10층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1195,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ir1x</t>
+          <t>https://talk.naver.com/ct/w5wqf8</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>323</v>
+        <v>132</v>
       </c>
       <c r="Q8" t="n">
-        <v>291</v>
+        <v>565</v>
       </c>
       <c r="R8" t="n">
-        <v>614</v>
+        <v>697</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1527157868</t>
+          <t>1442656447</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1527157868</t>
+          <t>https://m.place.naver.com/place/1442656447</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1307,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1598</v>
+        <v>1601</v>
       </c>
       <c r="Q9" t="n">
         <v>999</v>
       </c>
       <c r="R9" t="n">
-        <v>2597</v>
+        <v>2600</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1332,7 +1336,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1434,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1503,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2697</v>
+        <v>2698</v>
       </c>
       <c r="Q11" t="n">
         <v>1033</v>
       </c>
       <c r="R11" t="n">
-        <v>3730</v>
+        <v>3731</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1528,7 +1532,105 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>위더핏 PT 동탄목동점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>wethefit@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1356-0494</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄순환대로20길 124 우성스타파크A 609호 위더핏 PT 동탄목동점</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4bnry</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>245</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>260</v>
+      </c>
+      <c r="R12" t="n">
+        <v>505</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1114041606</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1114041606</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
